--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104605_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104605_W17.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3767</v>
+        <v>6.9664</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0621</v>
+        <v>4.2818</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3146</v>
+        <v>2.6846</v>
       </c>
       <c r="G2" t="n">
-        <v>3.0684</v>
+        <v>3.0506</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2873</v>
+        <v>-0.279</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3557</v>
+        <v>3.3296</v>
       </c>
       <c r="J2" t="n">
-        <v>2.909</v>
+        <v>2.8467</v>
       </c>
       <c r="K2" t="n">
+        <v>0.1821</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2.6646</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.2038</v>
       </c>
-      <c r="L2" t="n">
-        <v>2.7052</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.1594</v>
-      </c>
       <c r="N2" t="n">
-        <v>-0.4911</v>
+        <v>-0.4612</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6505</v>
+        <v>0.665</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.722</v>
+        <v>-2.7316</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4023</v>
+        <v>0.2162</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6563</v>
+        <v>-0.349</v>
       </c>
       <c r="U2" t="n">
-        <v>0.254</v>
+        <v>0.5652</v>
       </c>
       <c r="V2" t="n">
-        <v>3.4837</v>
+        <v>3.472</v>
       </c>
       <c r="W2" t="n">
-        <v>4.5314</v>
+        <v>4.5157</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0477</v>
+        <v>-1.0436</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8379</v>
+        <v>3.3034</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08400000000000001</v>
+        <v>-0.1159</v>
       </c>
       <c r="F3" t="n">
-        <v>3.7539</v>
+        <v>3.4193</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9859</v>
+        <v>2.8147</v>
       </c>
       <c r="H3" t="n">
-        <v>0.482</v>
+        <v>-0.0987</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5038</v>
+        <v>2.9135</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7585</v>
+        <v>2.0517</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6092</v>
+        <v>0.1756</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1493</v>
+        <v>1.8761</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2274</v>
+        <v>0.763</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1272</v>
+        <v>-0.2744</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3546</v>
+        <v>1.0374</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-1.5934</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2169</v>
+        <v>0.077</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5939</v>
+        <v>-0.5742</v>
       </c>
       <c r="U3" t="n">
-        <v>0.623</v>
+        <v>0.6512</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5425</v>
+        <v>-0.4989</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.5425</v>
+        <v>-0.4989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.001</v>
+        <v>2.2327</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7433999999999999</v>
+        <v>-1.2355</v>
       </c>
       <c r="F4" t="n">
-        <v>3.7443</v>
+        <v>3.4682</v>
       </c>
       <c r="G4" t="n">
-        <v>2.8001</v>
+        <v>0.9867</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1186</v>
+        <v>0.477</v>
       </c>
       <c r="I4" t="n">
-        <v>2.9187</v>
+        <v>0.5097</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0784</v>
+        <v>0.7415</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1834</v>
+        <v>0.5926</v>
       </c>
       <c r="L4" t="n">
-        <v>1.895</v>
+        <v>0.1489</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7217</v>
+        <v>0.2452</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.302</v>
+        <v>-0.1155</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0237</v>
+        <v>0.3608</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5878</v>
+        <v>-2.2763</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4952</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2051</v>
+        <v>0.6086</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.234</v>
+        <v>0.2993</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0289</v>
+        <v>0.3093</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5014</v>
+        <v>1.5479</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5014</v>
+        <v>1.5479</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. WALDEN</t>
+          <t>M. EJIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4848</v>
+        <v>1.1153</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.0613</v>
+        <v>-1.4785</v>
       </c>
       <c r="F5" t="n">
-        <v>4.5461</v>
+        <v>2.5938</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4347</v>
+        <v>1.1703</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.2743</v>
+        <v>1.7661</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8397</v>
+        <v>-0.5958</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5772</v>
+        <v>0.5379</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6491</v>
+        <v>1.9683</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07190000000000001</v>
+        <v>-1.4303</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1425</v>
+        <v>0.6324</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3748</v>
+        <v>-0.2022</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7678</v>
+        <v>0.8345</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2268</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.722</v>
+        <v>-3.6421</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1013</v>
+        <v>-0.1416</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3085</v>
+        <v>-0.5532</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4098</v>
+        <v>0.4116</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5913</v>
+        <v>1.6801</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5463</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>0.045</v>
+        <v>-0.4989</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. EJIM</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4606</v>
+        <v>0.8804999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.9084</v>
+        <v>-1.5064</v>
       </c>
       <c r="F6" t="n">
-        <v>2.369</v>
+        <v>2.3869</v>
       </c>
       <c r="G6" t="n">
-        <v>1.1647</v>
+        <v>1.107</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7618</v>
+        <v>0.723</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5971</v>
+        <v>0.384</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5609</v>
+        <v>0.3892</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9843</v>
+        <v>0.8963</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.4234</v>
+        <v>-0.5071</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6038</v>
+        <v>0.7178</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2225</v>
+        <v>-0.1733</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8264</v>
+        <v>0.8911</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.5878</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.6293</v>
+        <v>-1.5934</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8003</v>
+        <v>-0.2739</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0253</v>
+        <v>-0.3022</v>
       </c>
       <c r="U6" t="n">
-        <v>0.225</v>
+        <v>0.0283</v>
       </c>
       <c r="V6" t="n">
-        <v>1.684</v>
+        <v>0.2751</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1853</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5014</v>
+        <v>0.2751</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>C. WALDEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4496</v>
+        <v>0.5817</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0488</v>
+        <v>-3.8524</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4008</v>
+        <v>4.4342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2032</v>
+        <v>-0.4167</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.0607</v>
+        <v>-1.2615</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2639</v>
+        <v>0.8448</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6317</v>
+        <v>-1.5954</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0346</v>
+        <v>-1.6622</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5971</v>
+        <v>0.0668</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4285</v>
+        <v>1.1787</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0954</v>
+        <v>0.4007</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3331</v>
+        <v>0.778</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-2.7316</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>2.9592</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.075</v>
+        <v>0.1802</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2299</v>
+        <v>-0.0702</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3049</v>
+        <v>0.2504</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3214</v>
+        <v>0.5906</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3214</v>
+        <v>0.5447</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2608</v>
+        <v>0.3041</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7189</v>
+        <v>-0.3644</v>
       </c>
       <c r="F8" t="n">
-        <v>1.9797</v>
+        <v>0.6685</v>
       </c>
       <c r="G8" t="n">
-        <v>1.1015</v>
+        <v>0.2162</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7097</v>
+        <v>-0.0522</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3918</v>
+        <v>0.2683</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4072</v>
+        <v>0.6303</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9005</v>
+        <v>0.0345</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.4932</v>
+        <v>0.5958</v>
       </c>
       <c r="M8" t="n">
-        <v>0.6943</v>
+        <v>-0.4141</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1908</v>
+        <v>-0.0866</v>
       </c>
       <c r="O8" t="n">
-        <v>0.885</v>
+        <v>-0.3275</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2268</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.5878</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8837</v>
+        <v>-0.2276</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5383</v>
+        <v>-0.1721</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3454</v>
+        <v>-0.0556</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2699</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4166</v>
+        <v>-0.5332</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9227</v>
+        <v>-0.9293</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5061</v>
+        <v>0.3961</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3603</v>
+        <v>0.3657</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8658</v>
+        <v>-0.8618</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2262</v>
+        <v>1.2275</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1893</v>
+        <v>-0.1939</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5496</v>
+        <v>0.5595</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6291</v>
+        <v>0.6317</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1379</v>
+        <v>-0.2647</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2099</v>
+        <v>0.0838</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3856</v>
+        <v>-0.387</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.7363</v>
+        <v>-0.6179</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4031</v>
+        <v>-1.1718</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6667999999999999</v>
+        <v>0.5538999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5589</v>
+        <v>0.5678</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0622</v>
+        <v>-0.055</v>
       </c>
       <c r="I10" t="n">
-        <v>0.6211</v>
+        <v>0.6227</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1666</v>
+        <v>0.1662</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3923</v>
+        <v>0.4016</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0684</v>
+        <v>0.0419</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>0.0278</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1403</v>
+        <v>0.0141</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="11">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7336</v>
+        <v>-2.0242</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.265</v>
+        <v>-2.4465</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5314</v>
+        <v>0.4223</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0161</v>
+        <v>-2.0149</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4301</v>
+        <v>-0.4253</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.586</v>
+        <v>-1.5896</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.4303</v>
+        <v>-1.4429</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.492</v>
+        <v>-0.4966</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.9383</v>
+        <v>-0.9463</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5858</v>
+        <v>-0.572</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2825</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>0.1345</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0169</v>
+        <v>-0.1438</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3936</v>
+        <v>-3.2448</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4537</v>
+        <v>-3.4148</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0601</v>
+        <v>0.1701</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4827</v>
+        <v>-2.4909</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.0878</v>
+        <v>-3.0957</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6051</v>
+        <v>0.6048</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.9238</v>
+        <v>-1.9465</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.3315</v>
+        <v>-2.3484</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.5444</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3911</v>
+        <v>-0.2287</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5565</v>
+        <v>-0.4879</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1654</v>
+        <v>0.2592</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.5913</v>
+        <v>8.963999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-12.2816</v>
+        <v>-12.2337</v>
       </c>
       <c r="F13" t="n">
-        <v>20.8728</v>
+        <v>21.1979</v>
       </c>
       <c r="G13" t="n">
-        <v>5.3095</v>
+        <v>5.356500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.2333</v>
+        <v>-3.1631</v>
       </c>
       <c r="I13" t="n">
-        <v>8.542900000000001</v>
+        <v>8.519500000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>2.391699999999999</v>
+        <v>2.1848</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3259</v>
+        <v>-1.430199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>3.7178</v>
+        <v>3.6151</v>
       </c>
       <c r="M13" t="n">
-        <v>2.9177</v>
+        <v>3.1715</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.9076</v>
+        <v>-1.7328</v>
       </c>
       <c r="O13" t="n">
-        <v>4.8254</v>
+        <v>4.9043</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.2808</v>
+        <v>-19.3488</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0126</v>
+        <v>17.0725</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3631000000000002</v>
+        <v>-0.02189999999999998</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.7522</v>
+        <v>-2.3957</v>
       </c>
       <c r="U13" t="n">
-        <v>2.3891</v>
+        <v>2.3737</v>
       </c>
       <c r="V13" t="n">
-        <v>5.9131</v>
+        <v>5.905900000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>7.359500000000001</v>
+        <v>7.3256</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.4465</v>
+        <v>-1.4198</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7341</v>
+        <v>2.1667</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0078</v>
+        <v>0.5937</v>
       </c>
       <c r="F14" t="n">
-        <v>2.7419</v>
+        <v>1.5729</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4933</v>
+        <v>2.0237</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9865</v>
+        <v>0.7128</v>
       </c>
       <c r="I14" t="n">
-        <v>0.4932</v>
+        <v>1.311</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2385</v>
+        <v>2.1204</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.9848</v>
+        <v>1.3165</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7463</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2548</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0017</v>
+        <v>-0.6037</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2531</v>
+        <v>0.5071</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.4952</v>
+        <v>-1.5934</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1757</v>
+        <v>2.9592</v>
       </c>
       <c r="S14" t="n">
-        <v>2.5469</v>
+        <v>0.1822</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6332</v>
+        <v>0.0668</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9137</v>
+        <v>0.1154</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.405</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0927</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3073</v>
+        <v>1.3604</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7457</v>
+        <v>-1.2392</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5616</v>
+        <v>2.5996</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0304</v>
+        <v>-0.5081</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7216</v>
+        <v>-1.0151</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3088</v>
+        <v>0.5071</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1521</v>
+        <v>-0.2839</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3365</v>
+        <v>-1.0287</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8156</v>
+        <v>0.7447</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1216</v>
+        <v>-0.2241</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6149</v>
+        <v>0.0135</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4932</v>
+        <v>-0.2377</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5878</v>
+        <v>-2.5039</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>0.33</v>
+        <v>1.1856</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1815</v>
+        <v>0.4592</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1485</v>
+        <v>0.7264</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.4141</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.4141</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8115</v>
+        <v>1.0823</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.274</v>
+        <v>-0.0384</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0855</v>
+        <v>1.1207</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4065</v>
+        <v>0.4076</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3892</v>
+        <v>0.3903</v>
       </c>
       <c r="J16" t="n">
-        <v>0.092</v>
+        <v>0.0917</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3145</v>
+        <v>0.3159</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0487</v>
+        <v>0.2195</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1391</v>
+        <v>0.0975</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. NZOSA</t>
+          <t>P. ALMAZAN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1382</v>
+        <v>0.5432</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2485</v>
+        <v>-0.8309</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1103</v>
+        <v>1.3741</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4504</v>
+        <v>-1.0418</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0981</v>
+        <v>0.4104</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-1.4522</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8312</v>
+        <v>-0.6145</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8312</v>
+        <v>0.1379</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.7524</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3808</v>
+        <v>-0.4273</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2669</v>
+        <v>0.2725</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6998</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.4537</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8154</v>
+        <v>0.2192</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6261</v>
+        <v>-0.2164</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1893</v>
+        <v>0.4356</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>Y. NZOSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2332</v>
+        <v>0.0547</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2826</v>
+        <v>-0.2552</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0494</v>
+        <v>0.3099</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6988</v>
+        <v>0.4566</v>
       </c>
       <c r="H18" t="n">
-        <v>2.1876</v>
+        <v>1.0999</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.8864</v>
+        <v>-0.6433</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.3695</v>
+        <v>0.8274</v>
       </c>
       <c r="K18" t="n">
-        <v>1.8906</v>
+        <v>0.8274</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.2601</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3293</v>
+        <v>-0.3708</v>
       </c>
       <c r="N18" t="n">
-        <v>0.297</v>
+        <v>0.2725</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6263</v>
+        <v>-0.6433</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.4952</v>
+        <v>-0.4553</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7585</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2177</v>
+        <v>-0.6273</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9762999999999999</v>
+        <v>-0.0022</v>
       </c>
       <c r="V18" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7997</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4441</v>
+        <v>-0.1918</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3708</v>
+        <v>-1.0599</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9267</v>
+        <v>0.8681</v>
       </c>
       <c r="G19" t="n">
-        <v>3.7371</v>
+        <v>3.7367</v>
       </c>
       <c r="H19" t="n">
-        <v>3.5238</v>
+        <v>3.5159</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2133</v>
+        <v>0.2208</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7601</v>
+        <v>3.7319</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3523</v>
+        <v>3.33</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4078</v>
+        <v>0.4019</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.023</v>
+        <v>0.0048</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1715</v>
+        <v>0.1859</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7976</v>
+        <v>-0.54</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0253</v>
+        <v>-0.6717</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2277</v>
+        <v>0.1317</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.2495</v>
+        <v>-2.2504</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.1568</v>
+        <v>-1.1609</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6483</v>
+        <v>-0.4521</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1407</v>
+        <v>-2.4547</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4924</v>
+        <v>2.0026</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.6398</v>
+        <v>-1.7049</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2816</v>
+        <v>2.183</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9214</v>
+        <v>-3.888</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7877</v>
+        <v>-1.4099</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0631</v>
+        <v>1.8681</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7247</v>
+        <v>-3.2779</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8521</v>
+        <v>-0.2951</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3446</v>
+        <v>0.3149</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1967</v>
+        <v>-0.61</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8147</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8308</v>
+        <v>0.5503</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6866</v>
+        <v>-0.3329</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1442</v>
+        <v>0.8832</v>
       </c>
       <c r="V20" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3214</v>
+        <v>1.792</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3856</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ALMAZAN</t>
+          <t>A. LIMA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.674</v>
+        <v>-1.4385</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6539</v>
+        <v>-1.4887</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9799</v>
+        <v>0.0503</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.05</v>
+        <v>-0.5572</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4054</v>
+        <v>-0.7896</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4554</v>
+        <v>0.2324</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6105</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1385</v>
+        <v>-0.7896</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.749</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.4395</v>
+        <v>0.1579</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2669</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.7063</v>
+        <v>0.1579</v>
       </c>
       <c r="P21" t="n">
-        <v>1.361</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0.6829</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.985</v>
+        <v>0.4343</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0434</v>
+        <v>0.3646</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0584</v>
+        <v>0.0697</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LIMA</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0895</v>
+        <v>-1.7103</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1291</v>
+        <v>-3.014</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0396</v>
+        <v>1.3037</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.5545</v>
+        <v>-2.6533</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7864</v>
+        <v>0.2679</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2319</v>
+        <v>-2.9211</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.7117</v>
+        <v>-1.8263</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.7864</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>-1.7359</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1573</v>
+        <v>-0.827</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>0.3583</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1573</v>
+        <v>-1.1852</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7864</v>
+        <v>-0.2148</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7168</v>
+        <v>-0.1375</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0696</v>
+        <v>-0.0774</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.8678</v>
+        <v>0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8678</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2678</v>
+        <v>-3.53</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9213</v>
+        <v>-2.7108</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3465</v>
+        <v>-0.8193</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0256</v>
+        <v>-0.0277</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9394</v>
+        <v>0.9392</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9649</v>
+        <v>-0.9668</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.042</v>
+        <v>-0.0597</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3739</v>
+        <v>0.3652</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4159</v>
+        <v>-0.4249</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0165</v>
+        <v>0.032</v>
       </c>
       <c r="N23" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.832</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.747</v>
+        <v>-0.5113</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.4171</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.9566</v>
+        <v>-2.9529</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.949</v>
+        <v>-5.7103</v>
       </c>
       <c r="E24" t="n">
-        <v>-9.5898</v>
+        <v>-8.6995</v>
       </c>
       <c r="F24" t="n">
-        <v>2.6408</v>
+        <v>2.9892</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.472</v>
+        <v>-5.488</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.1685</v>
+        <v>-4.1783</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.3035</v>
+        <v>-1.3096</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.9931</v>
+        <v>-5.0334</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.1986</v>
+        <v>-4.2207</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7945</v>
+        <v>-0.8126</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4789</v>
+        <v>-0.4546</v>
       </c>
       <c r="N24" t="n">
-        <v>0.0301</v>
+        <v>0.0424</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R24" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4109</v>
+        <v>-0.1524</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.8086</v>
+        <v>-0.8647</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3977</v>
+        <v>0.7123</v>
       </c>
       <c r="V24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.591200000000001</v>
+        <v>-7.8257</v>
       </c>
       <c r="E25" t="n">
-        <v>-20.8728</v>
+        <v>-21.1976</v>
       </c>
       <c r="F25" t="n">
-        <v>12.2816</v>
+        <v>13.3718</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.309600000000001</v>
+        <v>-5.356400000000002</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2334</v>
+        <v>3.1633</v>
       </c>
       <c r="I25" t="n">
-        <v>-8.542900000000001</v>
+        <v>-8.519400000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.9176</v>
+        <v>-3.1715</v>
       </c>
       <c r="K25" t="n">
-        <v>1.907400000000001</v>
+        <v>1.7329</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.8253</v>
+        <v>-4.904199999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.3917</v>
+        <v>-2.185</v>
       </c>
       <c r="N25" t="n">
-        <v>1.3259</v>
+        <v>1.4303</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.7176</v>
+        <v>-3.6151</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.0125</v>
+        <v>-17.0723</v>
       </c>
       <c r="R25" t="n">
-        <v>19.2809</v>
+        <v>19.3487</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3630000000000002</v>
+        <v>1.1602</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.3891</v>
+        <v>-2.3737</v>
       </c>
       <c r="U25" t="n">
-        <v>2.7522</v>
+        <v>3.5338</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.913099999999999</v>
+        <v>-5.9058</v>
       </c>
       <c r="W25" t="n">
-        <v>1.4465</v>
+        <v>1.42</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.3597</v>
+        <v>-7.325699999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104605_W17.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104605_W17.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.0436</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.4989</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>1.5479</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.4989</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.2751</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.0458</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-1.4198</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104605_W17.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.325699999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
